--- a/artfynd/A 55278-2025 artfynd.xlsx
+++ b/artfynd/A 55278-2025 artfynd.xlsx
@@ -790,7 +790,7 @@
         <v>130016938</v>
       </c>
       <c r="B3" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -897,7 +897,7 @@
         <v>130016612</v>
       </c>
       <c r="B4" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1004,7 +1004,7 @@
         <v>130017066</v>
       </c>
       <c r="B5" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1108,10 +1108,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>130017081</v>
+        <v>130016914</v>
       </c>
       <c r="B6" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1143,10 +1143,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>570312</v>
+        <v>570402</v>
       </c>
       <c r="R6" t="n">
-        <v>6740715</v>
+        <v>6740598</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1178,7 +1178,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1188,12 +1188,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>14:12</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Mycket gamla tallar på holmen.</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1220,10 +1215,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>130016914</v>
+        <v>130017081</v>
       </c>
       <c r="B7" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1255,10 +1250,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>570402</v>
+        <v>570312</v>
       </c>
       <c r="R7" t="n">
-        <v>6740598</v>
+        <v>6740715</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1290,7 +1285,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1300,7 +1295,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>14:12</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Mycket gamla tallar på holmen.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1327,10 +1327,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>130016353</v>
+        <v>130016775</v>
       </c>
       <c r="B8" t="n">
-        <v>98797</v>
+        <v>98798</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1357,12 +1357,12 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -1376,10 +1376,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>570218</v>
+        <v>570405</v>
       </c>
       <c r="R8" t="n">
-        <v>6740496</v>
+        <v>6740539</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1411,7 +1411,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1421,7 +1421,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>13:52</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Spridda över ytan.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1448,10 +1453,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>130016775</v>
+        <v>130016353</v>
       </c>
       <c r="B9" t="n">
-        <v>98797</v>
+        <v>98798</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1478,12 +1483,12 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -1497,10 +1502,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>570405</v>
+        <v>570218</v>
       </c>
       <c r="R9" t="n">
-        <v>6740539</v>
+        <v>6740496</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1532,7 +1537,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1542,12 +1547,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>13:52</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Spridda över ytan.</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1577,7 +1577,7 @@
         <v>130016582</v>
       </c>
       <c r="B10" t="n">
-        <v>79182</v>
+        <v>79183</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1684,7 +1684,7 @@
         <v>130017185</v>
       </c>
       <c r="B11" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1793,10 +1793,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>130016680</v>
+        <v>130017176</v>
       </c>
       <c r="B12" t="n">
-        <v>78844</v>
+        <v>79088</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1804,21 +1804,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1828,10 +1828,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>570367</v>
+        <v>570328</v>
       </c>
       <c r="R12" t="n">
-        <v>6740529</v>
+        <v>6740610</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1863,7 +1863,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1873,7 +1873,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1900,10 +1900,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>130017176</v>
+        <v>130016680</v>
       </c>
       <c r="B13" t="n">
-        <v>79087</v>
+        <v>78845</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1911,21 +1911,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1935,10 +1935,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>570328</v>
+        <v>570367</v>
       </c>
       <c r="R13" t="n">
-        <v>6740610</v>
+        <v>6740529</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1970,7 +1970,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1980,7 +1980,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2010,7 +2010,7 @@
         <v>130016886</v>
       </c>
       <c r="B14" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2122,7 +2122,7 @@
         <v>130016661</v>
       </c>
       <c r="B15" t="n">
-        <v>91605</v>
+        <v>91606</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2229,7 +2229,7 @@
         <v>130016343</v>
       </c>
       <c r="B16" t="n">
-        <v>98797</v>
+        <v>98798</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2467,7 +2467,7 @@
         <v>130015183</v>
       </c>
       <c r="B18" t="n">
-        <v>79182</v>
+        <v>79183</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2571,10 +2571,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>130015381</v>
+        <v>130016707</v>
       </c>
       <c r="B19" t="n">
-        <v>81072</v>
+        <v>79088</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2582,21 +2582,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1049</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2606,10 +2606,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>570050</v>
+        <v>570384</v>
       </c>
       <c r="R19" t="n">
-        <v>6740610</v>
+        <v>6740536</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2641,7 +2641,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2651,7 +2651,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2678,10 +2678,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>130016707</v>
+        <v>130015381</v>
       </c>
       <c r="B20" t="n">
-        <v>79087</v>
+        <v>81073</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2689,21 +2689,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>1049</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2713,10 +2713,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>570384</v>
+        <v>570050</v>
       </c>
       <c r="R20" t="n">
-        <v>6740536</v>
+        <v>6740610</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2748,7 +2748,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2758,7 +2758,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2788,7 +2788,7 @@
         <v>130015356</v>
       </c>
       <c r="B21" t="n">
-        <v>78844</v>
+        <v>78845</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2895,7 +2895,7 @@
         <v>130017072</v>
       </c>
       <c r="B22" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2999,59 +2999,45 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>130016229</v>
+        <v>130017062</v>
       </c>
       <c r="B23" t="n">
-        <v>98797</v>
+        <v>79088</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Falklotta, Falklotta, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>570207</v>
+        <v>570318</v>
       </c>
       <c r="R23" t="n">
-        <v>6740490</v>
+        <v>6740720</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3083,7 +3069,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3093,12 +3079,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>13:11</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>En överblommad.</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3125,45 +3106,59 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>130017062</v>
+        <v>130016229</v>
       </c>
       <c r="B24" t="n">
-        <v>79087</v>
+        <v>98798</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Falklotta, Falklotta, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>570318</v>
+        <v>570207</v>
       </c>
       <c r="R24" t="n">
-        <v>6740720</v>
+        <v>6740490</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3195,7 +3190,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3205,7 +3200,12 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>13:11</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>En överblommad.</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3232,45 +3232,59 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>130017139</v>
+        <v>130017158</v>
       </c>
       <c r="B25" t="n">
-        <v>79087</v>
+        <v>98798</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Falklotta, Falklotta, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>570338</v>
+        <v>570328</v>
       </c>
       <c r="R25" t="n">
-        <v>6740666</v>
+        <v>6740627</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3302,7 +3316,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3312,7 +3326,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3339,59 +3353,45 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>130017158</v>
+        <v>130017139</v>
       </c>
       <c r="B26" t="n">
-        <v>98797</v>
+        <v>79088</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K26" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Falklotta, Falklotta, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>570328</v>
+        <v>570338</v>
       </c>
       <c r="R26" t="n">
-        <v>6740627</v>
+        <v>6740666</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3423,7 +3423,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3433,7 +3433,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3463,7 +3463,7 @@
         <v>130016856</v>
       </c>
       <c r="B27" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>

--- a/artfynd/A 55278-2025 artfynd.xlsx
+++ b/artfynd/A 55278-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>130016899</v>
+        <v>130016938</v>
       </c>
       <c r="B2" t="n">
-        <v>57737</v>
+        <v>79088</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,39 +686,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Falklotta, Falklotta, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>570402</v>
+        <v>570364</v>
       </c>
       <c r="R2" t="n">
-        <v>6740597</v>
+        <v>6740618</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -750,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>130016938</v>
+        <v>130016899</v>
       </c>
       <c r="B3" t="n">
-        <v>79088</v>
+        <v>57737</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -798,34 +793,39 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Falklotta, Falklotta, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>570364</v>
+        <v>570402</v>
       </c>
       <c r="R3" t="n">
-        <v>6740618</v>
+        <v>6740597</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -857,7 +857,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -867,7 +867,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -2571,10 +2571,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>130016707</v>
+        <v>130015381</v>
       </c>
       <c r="B19" t="n">
-        <v>79088</v>
+        <v>81073</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2582,21 +2582,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>1049</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2606,10 +2606,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>570384</v>
+        <v>570050</v>
       </c>
       <c r="R19" t="n">
-        <v>6740536</v>
+        <v>6740610</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2641,7 +2641,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2651,7 +2651,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2678,10 +2678,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>130015381</v>
+        <v>130016707</v>
       </c>
       <c r="B20" t="n">
-        <v>81073</v>
+        <v>79088</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2689,21 +2689,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1049</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2713,10 +2713,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>570050</v>
+        <v>570384</v>
       </c>
       <c r="R20" t="n">
-        <v>6740610</v>
+        <v>6740536</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2748,7 +2748,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2758,7 +2758,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2785,10 +2785,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>130015356</v>
+        <v>130017072</v>
       </c>
       <c r="B21" t="n">
-        <v>78845</v>
+        <v>79088</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2796,21 +2796,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2820,10 +2820,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>570033</v>
+        <v>570312</v>
       </c>
       <c r="R21" t="n">
-        <v>6740623</v>
+        <v>6740717</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2855,7 +2855,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2865,7 +2865,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2892,10 +2892,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>130017072</v>
+        <v>130015356</v>
       </c>
       <c r="B22" t="n">
-        <v>79088</v>
+        <v>78845</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2903,21 +2903,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2927,10 +2927,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>570312</v>
+        <v>570033</v>
       </c>
       <c r="R22" t="n">
-        <v>6740717</v>
+        <v>6740623</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -2962,7 +2962,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2972,7 +2972,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AD22" t="b">

--- a/artfynd/A 55278-2025 artfynd.xlsx
+++ b/artfynd/A 55278-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>130016938</v>
+        <v>130016899</v>
       </c>
       <c r="B2" t="n">
-        <v>79088</v>
+        <v>57737</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,34 +686,39 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Falklotta, Falklotta, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>570364</v>
+        <v>570402</v>
       </c>
       <c r="R2" t="n">
-        <v>6740618</v>
+        <v>6740597</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -745,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -755,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>130016899</v>
+        <v>130016938</v>
       </c>
       <c r="B3" t="n">
-        <v>57737</v>
+        <v>79088</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -793,39 +798,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Falklotta, Falklotta, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>570402</v>
+        <v>570364</v>
       </c>
       <c r="R3" t="n">
-        <v>6740597</v>
+        <v>6740618</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -857,7 +857,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -867,7 +867,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -2785,10 +2785,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>130017072</v>
+        <v>130015356</v>
       </c>
       <c r="B21" t="n">
-        <v>79088</v>
+        <v>78845</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2796,21 +2796,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2820,10 +2820,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>570312</v>
+        <v>570033</v>
       </c>
       <c r="R21" t="n">
-        <v>6740717</v>
+        <v>6740623</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2855,7 +2855,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2865,7 +2865,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2892,10 +2892,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>130015356</v>
+        <v>130017072</v>
       </c>
       <c r="B22" t="n">
-        <v>78845</v>
+        <v>79088</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2903,21 +2903,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2927,10 +2927,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>570033</v>
+        <v>570312</v>
       </c>
       <c r="R22" t="n">
-        <v>6740623</v>
+        <v>6740717</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -2962,7 +2962,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2972,7 +2972,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2999,45 +2999,59 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>130017062</v>
+        <v>130016229</v>
       </c>
       <c r="B23" t="n">
-        <v>79088</v>
+        <v>98798</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Falklotta, Falklotta, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>570318</v>
+        <v>570207</v>
       </c>
       <c r="R23" t="n">
-        <v>6740720</v>
+        <v>6740490</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3069,7 +3083,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3079,7 +3093,12 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>13:11</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>En överblommad.</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3106,59 +3125,45 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>130016229</v>
+        <v>130017062</v>
       </c>
       <c r="B24" t="n">
-        <v>98798</v>
+        <v>79088</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Falklotta, Falklotta, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>570207</v>
+        <v>570318</v>
       </c>
       <c r="R24" t="n">
-        <v>6740490</v>
+        <v>6740720</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3190,7 +3195,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3200,12 +3205,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>13:11</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>En överblommad.</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AD24" t="b">

--- a/artfynd/A 55278-2025 artfynd.xlsx
+++ b/artfynd/A 55278-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>130016899</v>
+        <v>130016938</v>
       </c>
       <c r="B2" t="n">
-        <v>57737</v>
+        <v>79089</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,39 +686,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Falklotta, Falklotta, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>570402</v>
+        <v>570364</v>
       </c>
       <c r="R2" t="n">
-        <v>6740597</v>
+        <v>6740618</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -750,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>130016938</v>
+        <v>130016899</v>
       </c>
       <c r="B3" t="n">
-        <v>79088</v>
+        <v>57737</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -798,34 +793,39 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Falklotta, Falklotta, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>570364</v>
+        <v>570402</v>
       </c>
       <c r="R3" t="n">
-        <v>6740618</v>
+        <v>6740597</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -857,7 +857,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -867,7 +867,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -894,10 +894,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>130016612</v>
+        <v>130017066</v>
       </c>
       <c r="B4" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -929,10 +929,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>570368</v>
+        <v>570315</v>
       </c>
       <c r="R4" t="n">
-        <v>6740503</v>
+        <v>6740718</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -964,7 +964,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -974,7 +974,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1001,10 +1001,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130017066</v>
+        <v>130016612</v>
       </c>
       <c r="B5" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1036,10 +1036,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>570315</v>
+        <v>570368</v>
       </c>
       <c r="R5" t="n">
-        <v>6740718</v>
+        <v>6740503</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1071,7 +1071,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1111,7 +1111,7 @@
         <v>130016914</v>
       </c>
       <c r="B6" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1218,7 +1218,7 @@
         <v>130017081</v>
       </c>
       <c r="B7" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1330,7 +1330,7 @@
         <v>130016775</v>
       </c>
       <c r="B8" t="n">
-        <v>98798</v>
+        <v>98815</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1456,7 +1456,7 @@
         <v>130016353</v>
       </c>
       <c r="B9" t="n">
-        <v>98798</v>
+        <v>98815</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1574,10 +1574,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>130016582</v>
+        <v>130017185</v>
       </c>
       <c r="B10" t="n">
-        <v>79183</v>
+        <v>79089</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1585,21 +1585,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>967</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Varglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Letharia vulpina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Hue</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1609,10 +1609,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>570369</v>
+        <v>570310</v>
       </c>
       <c r="R10" t="n">
-        <v>6740462</v>
+        <v>6740615</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1644,7 +1644,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>13:37</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1654,7 +1654,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>13:37</t>
+          <t>14:21</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>På mycket gammal tall.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1681,10 +1686,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>130017185</v>
+        <v>130016582</v>
       </c>
       <c r="B11" t="n">
-        <v>79088</v>
+        <v>79184</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1692,21 +1697,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>967</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Varglav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Letharia vulpina</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hue</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1716,10 +1721,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>570310</v>
+        <v>570369</v>
       </c>
       <c r="R11" t="n">
-        <v>6740615</v>
+        <v>6740462</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1751,7 +1756,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>13:37</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1761,12 +1766,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>14:21</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>På mycket gammal tall.</t>
+          <t>13:37</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1796,7 +1796,7 @@
         <v>130017176</v>
       </c>
       <c r="B12" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1903,7 +1903,7 @@
         <v>130016680</v>
       </c>
       <c r="B13" t="n">
-        <v>78845</v>
+        <v>78846</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2010,7 +2010,7 @@
         <v>130016886</v>
       </c>
       <c r="B14" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2122,7 +2122,7 @@
         <v>130016661</v>
       </c>
       <c r="B15" t="n">
-        <v>91606</v>
+        <v>91623</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2229,7 +2229,7 @@
         <v>130016343</v>
       </c>
       <c r="B16" t="n">
-        <v>98798</v>
+        <v>98815</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2467,7 +2467,7 @@
         <v>130015183</v>
       </c>
       <c r="B18" t="n">
-        <v>79183</v>
+        <v>79184</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2571,10 +2571,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>130015381</v>
+        <v>130016707</v>
       </c>
       <c r="B19" t="n">
-        <v>81073</v>
+        <v>79089</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2582,21 +2582,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1049</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2606,10 +2606,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>570050</v>
+        <v>570384</v>
       </c>
       <c r="R19" t="n">
-        <v>6740610</v>
+        <v>6740536</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2641,7 +2641,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2651,7 +2651,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2678,10 +2678,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>130016707</v>
+        <v>130015381</v>
       </c>
       <c r="B20" t="n">
-        <v>79088</v>
+        <v>81074</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2689,21 +2689,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>1049</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2713,10 +2713,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>570384</v>
+        <v>570050</v>
       </c>
       <c r="R20" t="n">
-        <v>6740536</v>
+        <v>6740610</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2748,7 +2748,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2758,7 +2758,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2788,7 +2788,7 @@
         <v>130015356</v>
       </c>
       <c r="B21" t="n">
-        <v>78845</v>
+        <v>78846</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2895,7 +2895,7 @@
         <v>130017072</v>
       </c>
       <c r="B22" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2999,59 +2999,45 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>130016229</v>
+        <v>130017062</v>
       </c>
       <c r="B23" t="n">
-        <v>98798</v>
+        <v>79089</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Falklotta, Falklotta, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>570207</v>
+        <v>570318</v>
       </c>
       <c r="R23" t="n">
-        <v>6740490</v>
+        <v>6740720</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3083,7 +3069,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3093,12 +3079,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>13:11</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>En överblommad.</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3125,45 +3106,59 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>130017062</v>
+        <v>130016229</v>
       </c>
       <c r="B24" t="n">
-        <v>79088</v>
+        <v>98815</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Falklotta, Falklotta, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>570318</v>
+        <v>570207</v>
       </c>
       <c r="R24" t="n">
-        <v>6740720</v>
+        <v>6740490</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3195,7 +3190,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3205,7 +3200,12 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>13:11</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>En överblommad.</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3235,7 +3235,7 @@
         <v>130017158</v>
       </c>
       <c r="B25" t="n">
-        <v>98798</v>
+        <v>98815</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3356,7 +3356,7 @@
         <v>130017139</v>
       </c>
       <c r="B26" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3463,7 +3463,7 @@
         <v>130016856</v>
       </c>
       <c r="B27" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
